--- a/RefractionApp/Refraction/Resources/SampleData/survival_data.xlsx
+++ b/RefractionApp/Refraction/Resources/SampleData/survival_data.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -422,13 +422,21 @@
           <t>Control</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr"/>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
       <c r="C1" t="inlineStr">
         <is>
           <t>Treatment</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr"/>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Treatment</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -454,55 +462,55 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2.4</v>
+        <v>5</v>
       </c>
       <c r="B5" t="n">
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>2.2</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2.6</v>
+        <v>7</v>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>3.4</v>
+        <v>8</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
@@ -510,13 +518,13 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2.6</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>7.3</v>
+        <v>10</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -524,13 +532,13 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>3.1</v>
+        <v>11</v>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>9.9</v>
+        <v>14</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -538,13 +546,13 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>3.3</v>
+        <v>13</v>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D9" t="n">
         <v>1</v>
@@ -552,13 +560,13 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>3.4</v>
+        <v>15</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>14.7</v>
+        <v>22</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -566,57 +574,29 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>4.5</v>
+        <v>18</v>
       </c>
       <c r="B11" t="n">
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>18.1</v>
+        <v>26</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>4.6</v>
+        <v>20</v>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>23.4</v>
+        <v>30</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="n">
-        <v>34.9</v>
-      </c>
-      <c r="D14" t="n">
         <v>0</v>
       </c>
     </row>
